--- a/Vysti Rules for Writing.xlsx
+++ b/Vysti Rules for Writing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,7 +2095,6 @@
           <t>After a quotation, include a parenthetical citation before the period. Use the format (Author Page), e.g., (Morrison 42). If you already named the author, just the page number is fine: (42).</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Citation format</t>
@@ -2104,6 +2103,33 @@
       <c r="F62" t="inlineStr">
         <is>
           <t>Review citation formatting after quotations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Avoid unnecessary repetition</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>When a student repeats the same word two or more times within a single sentence, the writing usually signals one of three weaknesses: a narrow active vocabulary, under-developed thinking that loops on the same idea, or weak organization that doesn't combine related thoughts cleanly. Three revision techniques resolve this: (1) Substitute a pronoun for the second reference when the antecedent is clear. (2) Choose a precise synonym, particularly when the repeated word is doing different conceptual work in each instance. (3) Restructure the sentence — use an appositive to fold the second reference into the first ('Hester, a woman shaped by shame, ...'), or subordinate one clause to the other. If the repetition is deliberate (anaphora, polysyndeton, or rhetorical emphasis), it should be intentional and serve a clear purpose; accidental repetition almost never does.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Replace one of the repeated words with a pronoun, a precise synonym, or rework the sentence so the idea is expressed more concisely. Try using an appositive — e.g., "Hester wore Hester's red letter" becomes "Hester wore the red letter, a mark of her shame." Repeating the same word usually means there's a way to tighten or clarify the prose.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Word choice</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Use a synonym or restructure to avoid repeating the same word within a sentence.</t>
         </is>
       </c>
     </row>
